--- a/问题4/灵敏度分析_参数扰动.xlsx
+++ b/问题4/灵敏度分析_参数扰动.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>同倍率改变充放电效率</t>
+          <t>同倍率改变充放电效率；对照基准为同 η 的固定电价缴费</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>同倍率改变功率上限</t>
+          <t>同倍率改变功率上限；对照基准为同 P̄ 的固定电价缴费</t>
         </is>
       </c>
     </row>
@@ -671,12 +671,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>翻转：①波动电价反而更便宜</t>
+          <t>不翻转（两项均成立）</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>同倍率改变充放电效率</t>
+          <t>同倍率改变充放电效率；对照基准为同 η 的固定电价缴费</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>同倍率改变功率上限</t>
+          <t>同倍率改变功率上限；对照基准为同 P̄ 的固定电价缴费</t>
         </is>
       </c>
     </row>
@@ -769,12 +769,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>翻转：①波动电价反而更便宜</t>
+          <t>不翻转（两项均成立）</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>同倍率改变充放电效率</t>
+          <t>同倍率改变充放电效率；对照基准为同 η 的固定电价缴费</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>同倍率改变功率上限</t>
+          <t>同倍率改变功率上限；对照基准为同 P̄ 的固定电价缴费</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>同倍率改变充放电效率</t>
+          <t>同倍率改变充放电效率；对照基准为同 η 的固定电价缴费</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>同倍率改变功率上限</t>
+          <t>同倍率改变功率上限；对照基准为同 P̄ 的固定电价缴费</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>同倍率改变充放电效率</t>
+          <t>同倍率改变充放电效率；对照基准为同 η 的固定电价缴费</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>同倍率改变功率上限</t>
+          <t>同倍率改变功率上限；对照基准为同 P̄ 的固定电价缴费</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>同倍率改变充放电效率</t>
+          <t>同倍率改变充放电效率；对照基准为同 η 的固定电价缴费</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>同倍率改变功率上限</t>
+          <t>同倍率改变功率上限；对照基准为同 P̄ 的固定电价缴费</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>V_E 整体乘 (1±pct%%)，等价于按比例缩放余值</t>
+          <t>V_E 整体乘 (1±该档%)，等价于按比例缩放余值</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>V_E 整体乘 (1±pct%%)，等价于按比例缩放余值</t>
+          <t>V_E 整体乘 (1±该档%)，等价于按比例缩放余值</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>V_E 整体乘 (1±pct%%)，等价于按比例缩放余值</t>
+          <t>V_E 整体乘 (1±该档%)，等价于按比例缩放余值</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>V_E 整体乘 (1±pct%%)，等价于按比例缩放余值</t>
+          <t>V_E 整体乘 (1±该档%)，等价于按比例缩放余值</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>V_E 整体乘 (1±pct%%)，等价于按比例缩放余值</t>
+          <t>V_E 整体乘 (1±该档%)，等价于按比例缩放余值</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>V_E 整体乘 (1±pct%%)，等价于按比例缩放余值</t>
+          <t>V_E 整体乘 (1±该档%)，等价于按比例缩放余值</t>
         </is>
       </c>
     </row>
